--- a/propuesta/TemplateRiesgos.xlsx
+++ b/propuesta/TemplateRiesgos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\Documents\Source\TrabajoFinalAUS\propuesta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E66036AD-AA98-4562-BB12-5FEF735C2838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885B6E25-F296-4ED6-B9D1-47F5398262EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HIR" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>Riesgo ID</t>
-  </si>
-  <si>
-    <t>Descripción (Condicion-Transición-Consecuencia)</t>
   </si>
   <si>
     <t>Categoría del riesgo</t>
@@ -84,16 +81,10 @@
     <t>19/10/2025</t>
   </si>
   <si>
-    <t>Crítico</t>
-  </si>
-  <si>
     <t>22/12/2025</t>
   </si>
   <si>
     <t xml:space="preserve">                         </t>
-  </si>
-  <si>
-    <t>Tamaño del Producto</t>
   </si>
   <si>
     <t>MMMR</t>
@@ -129,16 +120,7 @@
     <t>Teo Baiocchi</t>
   </si>
   <si>
-    <t>Dado que existe rotación de personal y se destinan recursos para capacitar gente nueva entonces hay preocupación por perder el tiempo y dinero del proyecto.</t>
-  </si>
-  <si>
     <t>1. Plan de mitigación comenzado</t>
-  </si>
-  <si>
-    <t>Subcondición 1: Los empleados reciben una mejor oferta de compensación en otras empresas.
-Subcondición 2: Las herramientas utilizadas en el proyecto no son utilizadas en entornos externos y no ofrecen ningún tipo de desarrollo personal en la carrera del empleado.
-Subcondición 3: Malas condiciones laborales (sillas inapropiadas, estaciones de trabajo con malos requerimientos).
-3. Los objetivos de los desarrolladores no son claros</t>
   </si>
   <si>
     <t>A-A100</t>
@@ -152,18 +134,43 @@
     <t>A-A101</t>
   </si>
   <si>
-    <t>1. Ofrecer tareas claras al equipo de desarrollo.
-2. Mejores compensaciones salariales, priorizandolas en lugar de darles más beneficios.
-3. Gestionar mejor los tiempo para obtener un entorno con menos presiones para el desarrollador</t>
-  </si>
-  <si>
-    <t>Dado que los avances de un sprint pueden llegar a ser muy grandes, existe la posibilidad de que las deadlines sean muy cortas y el equipo sufra gran presión entonces hay preocupación por el bienestar del equipo</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
     <t>Matias Barki</t>
+  </si>
+  <si>
+    <t>Descripción (CTC)</t>
+  </si>
+  <si>
+    <t>Subcondición 1: Los empleados reciben una mejor oferta de compensación en otras empresas.
+Subcondición 2: Las herramientas utilizadas en el proyecto no son utilizadas en entornos externos y no ofrecen ningún tipo de desarrollo personal en la carrera del empleado.
+Subcondición 3: Malas condiciones laborales (estaciones de trabajo antiguas, escritorios pequeños, sillas inapropiadas).
+3. Los objetivos de los desarrolladores no son claros.</t>
+  </si>
+  <si>
+    <t>1. Ofrecer tareas claras al equipo de desarrollo.
+2. Mejores compensaciones salariales, priorizandolas en lugar de darles más beneficios.
+3. Gestionar mejor los tiempo para obtener un entorno con menos presiones para el desarrollador.
+4. Revisiones de pares para poder poner al dia al resto del equipo.</t>
+  </si>
+  <si>
+    <t>Dado que los sprint pueden llegar a ser muy cortos, existe la posibilidad de que el equipo sufra gran presión y se vea afectado su bienestar.</t>
+  </si>
+  <si>
+    <t>Dado que existe rotación de personal y se destinan recursos para capacitar gente nueva entonces hay preocupación por perder el recursos destinados al proyecto.</t>
+  </si>
+  <si>
+    <t>Dado que el cliente puede pedir que se acelere el cronograma del proyecto, incluso habiendolo pactado previamente, entonces todo el equipo puede sufrir presión por intentar cumplir con las expectativas del cliente.</t>
+  </si>
+  <si>
+    <t>Dado que un componente puede estar documentado de manera incompleta o errónea por parte de los Analistas existe de que el equipo de Desarrollo pierda tiempo desarrollando funcionalidades que no fueron realmente pedidas o no se condicen con lo que el cliente pidio en un principio.</t>
+  </si>
+  <si>
+    <t>Dado que los repositorios de codigo ofrecidos por compañías (como Github, de Microsoft) pueden ser inaccesibes (por caídas de sus servicios, falta de acceso a la internet), existe la posibilidad de que los desarrolladores no puedan colaborar realizando revisiones de codigo (Pull Requests)</t>
+  </si>
+  <si>
+    <t>Estrategia</t>
   </si>
 </sst>
 </file>
@@ -248,7 +255,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -273,9 +280,6 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -283,9 +287,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -298,6 +299,15 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -530,71 +540,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
+      <c r="A1" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>20</v>
+      <c r="L2" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="4">
         <v>25000</v>
@@ -606,35 +616,35 @@
         <f>E3*F3</f>
         <v>17500</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="18" t="s">
+      <c r="H3" s="1">
+        <v>4</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
+      <c r="L3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
     </row>
     <row r="4" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="19">
+        <v>26</v>
+      </c>
+      <c r="D4" s="17">
         <v>46001</v>
       </c>
       <c r="E4" s="4">
@@ -647,36 +657,36 @@
         <f>E4*F4</f>
         <v>21600</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="18" t="s">
+      <c r="H4" s="1">
+        <v>2</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
+      <c r="L4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4">
         <v>32543</v>
@@ -688,40 +698,63 @@
         <f>E5*F5</f>
         <v>26034.400000000001</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="17" t="s">
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-    </row>
-    <row r="6" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D6" s="7"/>
+      <c r="K5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="B6" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="7">
+        <v>46179</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D7" s="7"/>
+    <row r="7" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B7" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="7">
+        <v>45669</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="B8" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D8" s="7"/>
       <c r="E8" s="8"/>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="20"/>
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9"/>
@@ -5681,14 +5714,14 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C5:C8" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Técnico,Empresarial,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H3:H5" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Catastrófico,Crítico,Marginal,Despreciable"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C4" xr:uid="{7B72F66F-2637-4046-A11A-9208F431911B}">
       <formula1>"Presupuestal,Técnico,Empresarial,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H3:H5" xr:uid="{96423B19-2231-408A-AA1D-90BC7100DBE7}">
+      <formula1>"4,3,2,1"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -5711,72 +5744,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="A1" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="3" spans="1:4" ht="229.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
-        <v>34</v>
+      <c r="A3" s="16" t="s">
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="18" t="s">
-        <v>36</v>
+      <c r="A4" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
-        <v>28</v>
+      <c r="A5" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D10" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/propuesta/TemplateRiesgos.xlsx
+++ b/propuesta/TemplateRiesgos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\Documents\Source\TrabajoFinalAUS\propuesta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885B6E25-F296-4ED6-B9D1-47F5398262EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F661BB9F-8ADA-4A3D-97D4-A29CDFF3F7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/propuesta/TemplateRiesgos.xlsx
+++ b/propuesta/TemplateRiesgos.xlsx
@@ -1,40 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\Documents\Source\TrabajoFinalAUS\propuesta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F661BB9F-8ADA-4A3D-97D4-A29CDFF3F7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4485" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="HIR" sheetId="1" r:id="rId1"/>
     <sheet name="MMMR" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
   <si>
     <t>Riesgo ID</t>
   </si>
@@ -161,26 +148,62 @@
     <t>Dado que existe rotación de personal y se destinan recursos para capacitar gente nueva entonces hay preocupación por perder el recursos destinados al proyecto.</t>
   </si>
   <si>
-    <t>Dado que el cliente puede pedir que se acelere el cronograma del proyecto, incluso habiendolo pactado previamente, entonces todo el equipo puede sufrir presión por intentar cumplir con las expectativas del cliente.</t>
-  </si>
-  <si>
-    <t>Dado que un componente puede estar documentado de manera incompleta o errónea por parte de los Analistas existe de que el equipo de Desarrollo pierda tiempo desarrollando funcionalidades que no fueron realmente pedidas o no se condicen con lo que el cliente pidio en un principio.</t>
-  </si>
-  <si>
     <t>Dado que los repositorios de codigo ofrecidos por compañías (como Github, de Microsoft) pueden ser inaccesibes (por caídas de sus servicios, falta de acceso a la internet), existe la posibilidad de que los desarrolladores no puedan colaborar realizando revisiones de codigo (Pull Requests)</t>
   </si>
   <si>
-    <t>Estrategia</t>
+    <t>Proyecto</t>
+  </si>
+  <si>
+    <t>P-A100</t>
+  </si>
+  <si>
+    <t>P-A101</t>
+  </si>
+  <si>
+    <t>Dado que el cliente puede pedir que se acelere el cronograma del proyecto, incluso habiendolo pactado previamente, todo el equipo puede sufrir presión por intentar cumplir con las expectativas del cliente.</t>
+  </si>
+  <si>
+    <t>Dado que un componente puede estar documentado de manera incompleta o errónea por parte de los Analistas existe la posibilidad de que el equipo de Desarrollo pierda tiempo desarrollando funcionalidades que no fueron realmente pedidas o no se condicen con lo que el cliente pidio en un principio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subcondición 1: El proceso de contrato es demasiado flexible.
+Subcondición 2: La tecnología no pasa por un análisis riguroso basado en el equipo actual y presupuesto antes de ser implementada.
+</t>
+  </si>
+  <si>
+    <t>1. Ofrecer tiempos de capacitación a los empleados.
+2. Obtener subscripciones a plataformas de capacitación
+3. Análisis riguroso por parte de los desarrolladores antes de implementar tecnologías nuevas, orientandolas a los tiempos esperados basados en el equipo y al presupuesto disponible.</t>
+  </si>
+  <si>
+    <t>&lt;En caso de que el proyecto haya comenzado&gt;
+1. Los Desarrolladores Seniors deben darle prioridad a la revisión de a pares debido que los Juniors tienen menos familiaridad o exposición a diferentes tecnologías.
+2. Los Analista deben comunicarle al cliente que las fechas límites serán desplazadas debido a que se destinará tiempo a la capacitación del personal.</t>
+  </si>
+  <si>
+    <t>Despreciable</t>
+  </si>
+  <si>
+    <t>Crítico</t>
+  </si>
+  <si>
+    <t>Marginal</t>
+  </si>
+  <si>
+    <t>Catastrófico</t>
+  </si>
+  <si>
+    <t>ID Impacto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -198,6 +221,13 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -255,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -300,18 +330,25 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -524,12 +561,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N999"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O999"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
@@ -539,23 +576,29 @@
     <col min="9" max="9" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-    </row>
-    <row r="2" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="N1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -592,8 +635,14 @@
       <c r="L2" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N2">
+        <v>4</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -601,7 +650,7 @@
         <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>14</v>
@@ -613,11 +662,11 @@
         <v>0.7</v>
       </c>
       <c r="G3" s="4">
-        <f>E3*F3</f>
+        <f t="shared" ref="G3:G8" si="0">E3*F3</f>
         <v>17500</v>
       </c>
       <c r="H3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>28</v>
@@ -632,9 +681,14 @@
         <v>18</v>
       </c>
       <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-    </row>
-    <row r="4" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N3" s="15">
+        <v>3</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -654,7 +708,7 @@
         <v>0.6</v>
       </c>
       <c r="G4" s="4">
-        <f>E4*F4</f>
+        <f t="shared" si="0"/>
         <v>21600</v>
       </c>
       <c r="H4" s="1">
@@ -673,9 +727,14 @@
         <v>18</v>
       </c>
       <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-    </row>
-    <row r="5" spans="1:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N4" s="15">
+        <v>2</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
@@ -692,11 +751,11 @@
         <v>32543</v>
       </c>
       <c r="F5" s="5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G5" s="4">
-        <f>E5*F5</f>
-        <v>26034.400000000001</v>
+        <f t="shared" si="0"/>
+        <v>19525.8</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
@@ -714,82 +773,120 @@
         <v>18</v>
       </c>
       <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="B6" s="20" t="s">
+      <c r="N5" s="15">
+        <v>1</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+      <c r="A6" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="17">
+        <v>46179</v>
+      </c>
+      <c r="E6" s="4">
+        <v>15000</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="7">
-        <v>46179</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="B7" s="20" t="s">
-        <v>39</v>
+      <c r="B7" s="18" t="s">
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="7">
+        <v>40</v>
+      </c>
+      <c r="D7" s="17">
         <v>45669</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
-      <c r="B8" s="20" t="s">
-        <v>41</v>
+      <c r="G7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+      <c r="B8" s="18" t="s">
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="17">
+        <v>46023</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B9" s="20"/>
+      <c r="G8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="18"/>
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D11" s="7"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D12" s="7"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D13" s="7"/>
       <c r="E13" s="8"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D14" s="7"/>
       <c r="E14" s="8"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D15" s="7"/>
       <c r="E15" s="8"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D16" s="7"/>
       <c r="E16" s="8"/>
       <c r="F16" s="9"/>
@@ -5714,29 +5811,30 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C5:C8" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Técnico,Empresarial,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C4" xr:uid="{7B72F66F-2637-4046-A11A-9208F431911B}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C4">
       <formula1>"Presupuestal,Técnico,Empresarial,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H3:H5" xr:uid="{96423B19-2231-408A-AA1D-90BC7100DBE7}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H3:H8">
       <formula1>"4,3,2,1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3 C5:C8">
+      <formula1>"Presupuestal,Proyecto,Técnico,Empresarial,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L3" location="MMMR!A3" display="Ver" xr:uid="{FCE42CD0-FD0B-46AF-A71A-A82E03D4F820}"/>
-    <hyperlink ref="L5" location="MMMR!A5" display="Ver" xr:uid="{F0B62E50-6BF9-4882-ACE8-E502EA1C7D43}"/>
-    <hyperlink ref="L4" location="MMMR!A4" display="Ver" xr:uid="{FFFCEF45-6E55-4A47-895A-CB441C914C3B}"/>
+    <hyperlink ref="L3" location="MMMR!A3" display="Ver"/>
+    <hyperlink ref="L5" location="MMMR!A5" display="Ver"/>
+    <hyperlink ref="L4" location="MMMR!A4" display="Ver"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95E0FF5-B58B-486C-8F0B-FABEE47F140B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="25.140625" customWidth="1"/>
@@ -5744,12 +5842,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -5780,7 +5878,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="23" t="s">
         <v>31</v>
       </c>
       <c r="B4" t="s">
@@ -5793,18 +5891,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="153" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
+      <c r="B5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -5817,10 +5915,11 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A3" location="HIR!A3" display="A-A100" xr:uid="{FAC28DB1-AA18-4AC8-AB38-2664160679C9}"/>
-    <hyperlink ref="A4" location="HIR!A4" display="A-A101" xr:uid="{D089AE2A-F3C2-4277-8FE3-F40CD16B66AD}"/>
-    <hyperlink ref="A5" location="HIR!A5" display="T-D100" xr:uid="{F2E25B4A-7FD7-4667-8A45-C13BEAB8D598}"/>
+    <hyperlink ref="A3" location="HIR!A3" display="A-A100"/>
+    <hyperlink ref="A4" location="HIR!A4" display="A-A101"/>
+    <hyperlink ref="A5" location="HIR!A5" display="T-D100"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/propuesta/TemplateRiesgos.xlsx
+++ b/propuesta/TemplateRiesgos.xlsx
@@ -1,27 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\Documents\Source\TrabajoFinalAUS\propuesta\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF5F9F0-C656-42B1-BA9A-4CC55BF2BBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4485" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HIR" sheetId="1" r:id="rId1"/>
     <sheet name="MMMR" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HIR!$A$2:$L$12</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="58">
   <si>
     <t>Riesgo ID</t>
   </si>
@@ -163,9 +179,6 @@
     <t>Dado que el cliente puede pedir que se acelere el cronograma del proyecto, incluso habiendolo pactado previamente, todo el equipo puede sufrir presión por intentar cumplir con las expectativas del cliente.</t>
   </si>
   <si>
-    <t>Dado que un componente puede estar documentado de manera incompleta o errónea por parte de los Analistas existe la posibilidad de que el equipo de Desarrollo pierda tiempo desarrollando funcionalidades que no fueron realmente pedidas o no se condicen con lo que el cliente pidio en un principio.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Subcondición 1: El proceso de contrato es demasiado flexible.
 Subcondición 2: La tecnología no pasa por un análisis riguroso basado en el equipo actual y presupuesto antes de ser implementada.
 </t>
@@ -193,17 +206,35 @@
     <t>Catastrófico</t>
   </si>
   <si>
-    <t>ID Impacto</t>
+    <t>T-D101</t>
+  </si>
+  <si>
+    <t>Dado que un componente puede estar documentado de manera incompleta, ambigua o errónea por parte de los Analistas existe la posibilidad de que el equipo de Desarrollo pierda tiempo desarrollando funcionalidades que no fueron realmente pedidas o no se condicen con lo que el cliente pidio en un principio.</t>
+  </si>
+  <si>
+    <t>Dado que el cliente puede presentar una quiebra, existe la posibilidad de que el proyecto quede discontinuado.</t>
+  </si>
+  <si>
+    <t>Dado que el cliente desee rescindir el contrato, existe la posibilidad de que el proyecto quede discontinuado.</t>
+  </si>
+  <si>
+    <t>Dado que el proyecto puede tardar demasiado tiempo, existe la posibilidad de que el cliente pueda encontrar otras soluciones que le sean utiles y el software desarrollado pierda su ventana de mercado, discontinuando el proyecto.</t>
+  </si>
+  <si>
+    <t>Dado que el cliente puede tener un cambio de enfoque en la logica de los procesos internos involucrados con el proyecto actual, este puede llegar a pedir un cambio en componentes que ya se consideraban estables.</t>
+  </si>
+  <si>
+    <t>Mercado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -228,6 +259,11 @@
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -285,7 +321,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -333,22 +369,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -561,12 +601,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:O999"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
@@ -577,24 +617,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="N1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
@@ -635,90 +673,66 @@
       <c r="L2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="N2">
-        <v>4</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="N2" s="22"/>
+      <c r="O2" s="24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="96.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="15"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>25000</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F4" s="5">
         <v>0.7</v>
       </c>
-      <c r="G3" s="4">
-        <f t="shared" ref="G3:G8" si="0">E3*F3</f>
+      <c r="G4" s="4">
+        <f>E4*F4</f>
         <v>17500</v>
       </c>
-      <c r="H3" s="1">
-        <v>3</v>
-      </c>
-      <c r="I3" s="14" t="s">
+      <c r="H4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J4" s="15" t="s">
         <v>22</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15">
-        <v>3</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="17">
-        <v>46001</v>
-      </c>
-      <c r="E4" s="4">
-        <v>36000</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="G4" s="4">
-        <f t="shared" si="0"/>
-        <v>21600</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>21</v>
@@ -727,68 +741,64 @@
         <v>18</v>
       </c>
       <c r="M4" s="15"/>
-      <c r="N4" s="15">
-        <v>2</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>50</v>
+      <c r="N4" s="22"/>
+      <c r="O4" s="25" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
+      </c>
+      <c r="D5" s="17">
+        <v>46001</v>
       </c>
       <c r="E5" s="4">
-        <v>32543</v>
+        <v>36000</v>
       </c>
       <c r="F5" s="5">
         <v>0.6</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
-        <v>19525.8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
+        <f>E5*F5</f>
+        <v>21600</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>32</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L5" s="16" t="s">
         <v>18</v>
       </c>
       <c r="M5" s="15"/>
-      <c r="N5" s="15">
-        <v>1</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="102" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
+      <c r="N5" s="23"/>
+      <c r="O5" s="25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="D6" s="17">
         <v>46179</v>
@@ -800,15 +810,18 @@
         <v>0.8</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>E6*F6</f>
         <v>12000</v>
       </c>
-      <c r="H6" s="1">
-        <v>1</v>
+      <c r="H6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B7" s="18" t="s">
@@ -823,14 +836,20 @@
       <c r="E7" s="8"/>
       <c r="F7" s="9"/>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>E7*F7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="1">
-        <v>1</v>
+      <c r="H7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="B8" s="18" t="s">
         <v>39</v>
       </c>
@@ -843,33 +862,96 @@
       <c r="E8" s="8"/>
       <c r="F8" s="9"/>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>E8*F8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B9" s="18"/>
+      <c r="H8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B9" s="18" t="s">
+        <v>53</v>
+      </c>
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B10" s="18" t="s">
+        <v>54</v>
+      </c>
       <c r="D10" s="7"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B11" s="18" t="s">
+        <v>56</v>
+      </c>
       <c r="D11" s="7"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
+      <c r="H11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4">
+        <v>32543</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="G12" s="4">
+        <f>E12*F12</f>
+        <v>19525.8</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D13" s="7"/>
@@ -5807,24 +5889,34 @@
       <c r="F999" s="9"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:L12" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L12">
+      <sortCondition ref="H3:H12" customList="Catastrófico,Crítico,Marginal,Despreciable"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L12">
+    <sortCondition ref="F3:F12"/>
+    <sortCondition ref="H3:H12"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C4">
-      <formula1>"Presupuestal,Técnico,Empresarial,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H3:H8">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N1:N4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"4,3,2,1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3 C5:C8">
-      <formula1>"Presupuestal,Proyecto,Técnico,Empresarial,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C9" xr:uid="{9969F3A2-8AC9-4A35-95E5-292F914BB602}">
+      <formula1>"Presupuestal,Proyecto,Técnico,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{85BFF8FB-489D-47FF-86DF-6D58013F86D9}">
+      <formula1>$O$2:$O$5</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L3" location="MMMR!A3" display="Ver"/>
-    <hyperlink ref="L5" location="MMMR!A5" display="Ver"/>
-    <hyperlink ref="L4" location="MMMR!A4" display="Ver"/>
+    <hyperlink ref="L5" location="MMMR!A4" display="Ver" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L12" location="MMMR!A5" display="Ver" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="L4" location="MMMR!A3" display="Ver" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5832,9 +5924,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="25.140625" customWidth="1"/>
@@ -5842,12 +5934,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -5878,7 +5970,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="19" t="s">
         <v>31</v>
       </c>
       <c r="B4" t="s">
@@ -5896,13 +5988,13 @@
         <v>25</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="D5" s="14" t="s">
         <v>46</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -5915,9 +6007,9 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A3" location="HIR!A3" display="A-A100"/>
-    <hyperlink ref="A4" location="HIR!A4" display="A-A101"/>
-    <hyperlink ref="A5" location="HIR!A5" display="T-D100"/>
+    <hyperlink ref="A3" location="HIR!A3" display="A-A100" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="A4" location="HIR!A4" display="A-A101" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="A5" location="HIR!A5" display="T-D100" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/propuesta/TemplateRiesgos.xlsx
+++ b/propuesta/TemplateRiesgos.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\Documents\Source\TrabajoFinalAUS\propuesta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\repos\TrabajoFinalAUS\propuesta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0D9A8C-8719-4807-9AF7-60D9369830F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304F45CD-E4CA-4FE3-8F81-F4C66FB1A4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HIR" sheetId="1" r:id="rId1"/>
     <sheet name="MMMR" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HIR!$A$2:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HIR!$A$2:$L$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="67">
   <si>
     <t>Riesgo ID</t>
   </si>
@@ -138,9 +138,6 @@
 3. Los objetivos de los desarrolladores no son claros.</t>
   </si>
   <si>
-    <t>Dado que los sprint pueden llegar a ser muy cortos, existe la posibilidad de que el equipo sufra gran presión y se vea afectado su bienestar.</t>
-  </si>
-  <si>
     <t>Dado que existe rotación de personal y se destinan recursos para capacitar gente nueva entonces hay preocupación por perder el recursos destinados al proyecto.</t>
   </si>
   <si>
@@ -151,12 +148,6 @@
   </si>
   <si>
     <t>P-A100</t>
-  </si>
-  <si>
-    <t>P-A101</t>
-  </si>
-  <si>
-    <t>Dado que el cliente puede pedir que se acelere el cronograma del proyecto, incluso habiendolo pactado previamente, todo el equipo puede sufrir presión por intentar cumplir con las expectativas del cliente.</t>
   </si>
   <si>
     <t xml:space="preserve">Subcondición 1: El proceso de contrato es demasiado flexible.
@@ -282,17 +273,34 @@
     <t>Dado que el framework de desarrollo frontend es muy reciente entonces hay preocupación porque el resto del equipo no esté capacitado para desarrollar con esta tecnologia de punta y se requieran mas recursos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Analista deben comunicarle al cliente que las fechas límites serán desplazadas, indicando que el personal subestimó la tarea. En realidad, se destinará tiempo a la capacitación del personal. </t>
-  </si>
-  <si>
     <t>1. Ofrecer tiempos de capacitación a los empleados.
 2. Obtener subscripciones a plataformas de capacitación
 3. Análisis riguroso por parte de los desarrolladores antes de implementar tecnologías nuevas, orientandolas a los tiempos esperados basados en el equipo y al presupuesto disponible.
 4. Los Desarrolladores Seniors deben darle prioridad a la revisión de a pares debido que los Juniors tienen menos familiaridad o exposición a diferentes tecnologías.
-5. Asignar más presupuesto para cubrir estas necesidades.</t>
-  </si>
-  <si>
-    <t>Subcondición 1: El Analista no consultó con los desarrolladores el tiempo que iba a tomar cada requisito</t>
+5. Asignar presupuesto donde corresponda para cubrir estas eventualidades.</t>
+  </si>
+  <si>
+    <t>Los Analista deben comunicarle al cliente que las fechas límites serán desplazadas, indicando que el personal calculó mal el tiempo para realizar estas tarea, se destinará tiempo a la capacitación del personal. 
+En caso de que el cliente no acepte extender el cronograma, ofrecer una tarifa plana en lugar de cobrar las horas de capacitación como horas trabajadas.
+Si el cliente aún así no quiere extender el cronograma, avisarle que el producto no poseerá determinados estándares de calidad.</t>
+  </si>
+  <si>
+    <t>Subcondición 1: El Analista no consultó con los desarrolladores el tiempo que iba a tomar cada requisito/funcionalidad.
+Subcondición 2: Los Desarrolladores estimaron menos tiempo del que realmente les iba a costar cada funcionalidad.
+Subcondición 3: Error durante el armado del cronograma por parte del Analista.
+Subcondición 3: El cliente puede tardar mucho tiempo en responder, pero pedir cambios de manera muy acelerada.</t>
+  </si>
+  <si>
+    <t>Extender el cronograma.
+En caso de que el cliente no acepte extender el cronograma, ofrecer una tarifa plana en lugar de cobrar las horas de capacitación como horas trabajadas.
+Si el cliente aún así no quiere extender el cronograma, avisarle que el producto no poseerá determinados estándares de calidad.</t>
+  </si>
+  <si>
+    <t>Dado que el cronograma puede llegar a ser muy corto, porque fue acelerado(por el cliente) o mal planeado desde un principio, existe la posibilidad de que el equipo sufra gran presión y se vea afectado su bienestar.</t>
+  </si>
+  <si>
+    <t>1. Realizar sugerencias al cliente sobre tiempos ideales para obtener un producto de calidad, y que riesgos se corren si estos estándares no se cumplen.
+2. Dejar por contrato que se va a cargar una tarifa por cada vez que se quiera realizar una modificación que achique el cronograma.</t>
   </si>
 </sst>
 </file>
@@ -382,7 +390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -405,21 +413,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -452,12 +451,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -470,47 +463,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -528,6 +509,62 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{014B851B-C4CB-5D4A-F08B-7F9407AC8AA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="0" y="4600575"/>
+          <a:ext cx="18973800" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -731,7 +768,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O999"/>
+  <dimension ref="A1:O998"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.42578125" customWidth="1"/>
@@ -743,20 +780,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
       <c r="N1" s="1"/>
       <c r="O1" t="s">
         <v>6</v>
@@ -801,17 +838,17 @@
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="A3" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="13">
@@ -824,40 +861,40 @@
         <v>0.8</v>
       </c>
       <c r="G3" s="2">
-        <f>E3*F3</f>
+        <f t="shared" ref="G3:G11" si="0">E3*F3</f>
         <v>12000</v>
       </c>
-      <c r="H3" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" s="19" t="s">
+      <c r="H3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="J3" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="18" t="str">
         <f>HYPERLINK("#MMMR!A" &amp; MATCH(A3, MMMR!A:A, 0), "Ver Migitacion, Monitoreo y Manejo")</f>
         <v>Ver Migitacion, Monitoreo y Manejo</v>
       </c>
       <c r="M3" s="12"/>
       <c r="N3" s="1"/>
       <c r="O3" s="12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>35</v>
+      <c r="B4" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>14</v>
@@ -869,39 +906,39 @@
         <v>0.7</v>
       </c>
       <c r="G4" s="2">
-        <f>E4*F4</f>
+        <f t="shared" si="0"/>
         <v>17500</v>
       </c>
-      <c r="H4" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="17" t="s">
+      <c r="H4" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="21" t="str">
+      <c r="L4" s="18" t="str">
         <f>HYPERLINK("#MMMR!A" &amp; MATCH(A4, MMMR!A:A, 0), "Ver Migitacion, Monitoreo y Manejo")</f>
         <v>Ver Migitacion, Monitoreo y Manejo</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="1"/>
       <c r="O4" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="13">
@@ -914,38 +951,38 @@
         <v>0.6</v>
       </c>
       <c r="G5" s="2">
-        <f>E5*F5</f>
+        <f t="shared" si="0"/>
         <v>21600</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="17" t="s">
+      <c r="H5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="21" t="str">
+      <c r="L5" s="18" t="str">
         <f>HYPERLINK("#MMMR!A" &amp; MATCH(A5, MMMR!A:A, 0), "Ver Migitacion, Monitoreo y Manejo")</f>
         <v>Ver Migitacion, Monitoreo y Manejo</v>
       </c>
       <c r="M5" s="12"/>
       <c r="O5" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="13" t="s">
@@ -958,183 +995,183 @@
         <v>0.6</v>
       </c>
       <c r="G6" s="2">
-        <f>E6*F6</f>
+        <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="H6" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="17" t="s">
+      <c r="H6" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="K6" s="19" t="s">
+      <c r="J6" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="21" t="str">
+      <c r="L6" s="18" t="str">
         <f>HYPERLINK("#MMMR!A" &amp; MATCH(A6, MMMR!A:A, 0), "Ver Migitacion, Monitoreo y Manejo")</f>
         <v>Ver Migitacion, Monitoreo y Manejo</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="29">
-        <v>45669</v>
-      </c>
-      <c r="E7" s="30">
-        <v>30000</v>
-      </c>
-      <c r="F7" s="31">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="30">
-        <f>E7*F7</f>
-        <v>15000</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="28" t="s">
+    <row r="7" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="13">
+        <v>45728</v>
+      </c>
+      <c r="E7" s="2">
+        <v>70000</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="0"/>
+        <v>10500</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="K7" s="32" t="s">
+      <c r="J7" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="L7" s="32"/>
-    </row>
-    <row r="8" spans="1:15" ht="102" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>35</v>
+      <c r="L7" s="17"/>
+    </row>
+    <row r="8" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="D8" s="13">
         <v>45728</v>
       </c>
       <c r="E8" s="2">
+        <v>200000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="17"/>
+    </row>
+    <row r="9" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="13">
+        <v>46023</v>
+      </c>
+      <c r="E9" s="2">
         <v>70000</v>
       </c>
-      <c r="F8" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G8" s="2">
-        <f>E8*F8</f>
-        <v>10500</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="17" t="s">
+      <c r="F9" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="K8" s="19" t="s">
+      <c r="J9" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="19"/>
-    </row>
-    <row r="9" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="17" t="s">
+      <c r="L9" s="17"/>
+    </row>
+    <row r="10" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="13">
+      <c r="B10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="13">
         <v>45728</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E10" s="2">
         <v>200000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="G9" s="2">
-        <f>E9*F9</f>
-        <v>10000</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="19"/>
-    </row>
-    <row r="10" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="13">
-        <v>46023</v>
-      </c>
-      <c r="E10" s="2">
-        <v>70000</v>
       </c>
       <c r="F10" s="3">
         <v>0.01</v>
       </c>
       <c r="G10" s="2">
-        <f>E10*F10</f>
-        <v>700</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="17" t="s">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="K10" s="19" t="s">
+      <c r="J10" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="19"/>
-    </row>
-    <row r="11" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>35</v>
+      <c r="L10" s="17"/>
+    </row>
+    <row r="11" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="D11" s="13">
         <v>45728</v>
@@ -1146,59 +1183,27 @@
         <v>0.01</v>
       </c>
       <c r="G11" s="2">
-        <f>E11*F11</f>
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="17" t="s">
+      <c r="H11" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="K11" s="19" t="s">
+      <c r="J11" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="19"/>
-    </row>
-    <row r="12" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="13">
-        <v>45728</v>
-      </c>
-      <c r="E12" s="2">
-        <v>200000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="G12" s="2">
-        <f>E12*F12</f>
-        <v>2000</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="K12" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="19"/>
+      <c r="L11" s="17"/>
+    </row>
+    <row r="12" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D13" s="5"/>
@@ -6130,21 +6135,16 @@
       <c r="E998" s="6"/>
       <c r="F998" s="7"/>
     </row>
-    <row r="999" spans="4:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D999" s="5"/>
-      <c r="E999" s="6"/>
-      <c r="F999" s="7"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:L12" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L12">
-      <sortCondition descending="1" ref="F3:F12"/>
-      <sortCondition ref="H3:H12" customList="Catastrófico,Crítico,Marginal,Despreciable"/>
+  <autoFilter ref="A2:L11" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L11">
+      <sortCondition descending="1" ref="F3:F11"/>
+      <sortCondition ref="H3:H11" customList="Catastrófico,Crítico,Marginal,Despreciable"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L12">
-    <sortCondition ref="F3:F12"/>
-    <sortCondition ref="H3:H12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L11">
+    <sortCondition ref="F3:F11"/>
+    <sortCondition ref="H3:H11"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -6154,15 +6154,16 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N1:N4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"4,3,2,1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C12" xr:uid="{9969F3A2-8AC9-4A35-95E5-292F914BB602}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C11" xr:uid="{9969F3A2-8AC9-4A35-95E5-292F914BB602}">
       <formula1>"Presupuestal,Proyecto,Técnico,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{85BFF8FB-489D-47FF-86DF-6D58013F86D9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H11" xr:uid="{85BFF8FB-489D-47FF-86DF-6D58013F86D9}">
       <formula1>$O$2:$O$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6177,75 +6178,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="357" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="339.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="339.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="216.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="23" t="s">
+      <c r="C5" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D5" s="19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="204" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="23" t="s">
+    <row r="6" spans="1:4" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">

--- a/propuesta/TemplateRiesgos.xlsx
+++ b/propuesta/TemplateRiesgos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\Documents\Source\TrabajoFinalAUS\propuesta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0D9A8C-8719-4807-9AF7-60D9369830F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669DA8F8-F2A1-41C1-8751-0CFB35455D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/propuesta/TemplateRiesgos.xlsx
+++ b/propuesta/TemplateRiesgos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\repos\TrabajoFinalAUS\propuesta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278ABD80-716E-49CD-B961-F37FEAD77E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1145AF2E-94D3-443B-B5BE-8CF99B51C33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HIR" sheetId="1" r:id="rId1"/>
